--- a/Dashboards/data/Data final/pobreza/Pobreza_tableau.xlsx
+++ b/Dashboards/data/Data final/pobreza/Pobreza_tableau.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="268" uniqueCount="9">
   <si>
     <t>ano</t>
   </si>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -205,7 +205,7 @@
         <v>2003</v>
       </c>
       <c r="B9" s="1">
-        <v>30.821599960327148</v>
+        <v>30.821599960327149</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -233,7 +233,7 @@
         <v>2003</v>
       </c>
       <c r="B11" s="1">
-        <v>50.432998657226562</v>
+        <v>50.432998657226563</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -317,7 +317,7 @@
         <v>2005</v>
       </c>
       <c r="B17" s="1">
-        <v>39.772598266601562</v>
+        <v>39.772598266601563</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -401,7 +401,7 @@
         <v>2007</v>
       </c>
       <c r="B23" s="1">
-        <v>33.382400512695312</v>
+        <v>33.382400512695313</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -527,7 +527,7 @@
         <v>2009</v>
       </c>
       <c r="B32" s="1">
-        <v>36.026199340820312</v>
+        <v>36.026199340820313</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
@@ -919,7 +919,7 @@
         <v>2013</v>
       </c>
       <c r="B60" s="1">
-        <v>17.636999130249023</v>
+        <v>17.636999130249024</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
@@ -1017,7 +1017,7 @@
         <v>2014</v>
       </c>
       <c r="B67" s="1">
-        <v>4.4840002059936523</v>
+        <v>4.4840002059936524</v>
       </c>
       <c r="C67" t="s">
         <v>4</v>
@@ -1157,7 +1157,7 @@
         <v>2016</v>
       </c>
       <c r="B77" s="1">
-        <v>17.468399047851562</v>
+        <v>17.468399047851563</v>
       </c>
       <c r="C77" t="s">
         <v>4</v>
@@ -1199,7 +1199,7 @@
         <v>2017</v>
       </c>
       <c r="B80" s="1">
-        <v>21.480300903320312</v>
+        <v>21.480300903320313</v>
       </c>
       <c r="C80" t="s">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         <v>2017</v>
       </c>
       <c r="B85" s="1">
-        <v>3.3097000122070312</v>
+        <v>3.3097000122070313</v>
       </c>
       <c r="C85" t="s">
         <v>4</v>
@@ -1409,7 +1409,7 @@
         <v>2019</v>
       </c>
       <c r="B95" s="1">
-        <v>18.631200790405273</v>
+        <v>18.631200790405274</v>
       </c>
       <c r="C95" t="s">
         <v>4</v>
@@ -1619,7 +1619,7 @@
         <v>2022</v>
       </c>
       <c r="B110" s="1">
-        <v>25.227300643920898</v>
+        <v>25.227300643920899</v>
       </c>
       <c r="C110" t="s">
         <v>3</v>
